--- a/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
+++ b/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
@@ -2,13 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="R9964dfbdfb4e4d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="R37d173ac1b7e404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="R7e746834a8964907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="R5f0e3d7550584015"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="PayrollHeader">'Payroll'!A12:AL12</x:definedName>
   </x:definedNames>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author/>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="C4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Source: SGP PayrollInput.xlsx, Payroll Input - August26, August 2026.
+Source: Zoho Payroll Singapore Configuration and Data Setup Pack, Compensation, Earning Codes, Deduction Codes and Statutory Config.
+SDL: https://www.cpf.gov.sg/employer/employer-obligations/skills-development-levy
+CPF eligibility and monthly review: https://www.cpf.gov.sg/employer/employer-obligations/who-should-receive-cpf-contributions
+CPF rates and ceilings: https://www.cpf.gov.sg/employer/employer-obligations/how-much-cpf-contributions-to-pay
+Only SDL is automated in this template. CPF, SHG fund eligibility, opt-outs and contribution amounts must be reviewed separately.
+Bonus, leave encashment, tax clearance, benefits, approval matrix, statutory filing and bank export are outside this monthly template.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -87,7 +110,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -154,9 +177,6 @@
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -485,7 +505,7 @@
       <x:c r="AK2" s="2"/>
       <x:c r="AL2" s="2"/>
     </x:row>
-    <x:row r="3" ht="35" customHeight="1">
+    <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -517,17 +537,15 @@
       <x:c r="AC3" s="2"/>
       <x:c r="AD3" s="2"/>
       <x:c r="AE3" s="2"/>
-      <x:c r="AF3" s="25" t="str">
-        <x:v>Source: SGP PayrollInput.xlsx, Payroll Input - August26, August 2026.</x:v>
-      </x:c>
-      <x:c r="AG3" s="25"/>
-      <x:c r="AH3" s="25"/>
-      <x:c r="AI3" s="25"/>
-      <x:c r="AJ3" s="25"/>
-      <x:c r="AK3" s="25"/>
-      <x:c r="AL3" s="25"/>
-    </x:row>
-    <x:row r="4" ht="35" customHeight="1">
+      <x:c r="AF3" s="2"/>
+      <x:c r="AG3" s="2"/>
+      <x:c r="AH3" s="2"/>
+      <x:c r="AI3" s="2"/>
+      <x:c r="AJ3" s="2"/>
+      <x:c r="AK3" s="2"/>
+      <x:c r="AL3" s="2"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="str">
         <x:v>SDL rate</x:v>
       </x:c>
@@ -571,17 +589,15 @@
       <x:c r="AC4" s="2"/>
       <x:c r="AD4" s="2"/>
       <x:c r="AE4" s="2"/>
-      <x:c r="AF4" s="25" t="str">
-        <x:v>Source: Zoho Payroll Singapore Configuration and Data Setup Pack, Compensation, Earning Codes, Deduction Codes and Statutory Config.</x:v>
-      </x:c>
-      <x:c r="AG4" s="25"/>
-      <x:c r="AH4" s="25"/>
-      <x:c r="AI4" s="25"/>
-      <x:c r="AJ4" s="25"/>
-      <x:c r="AK4" s="25"/>
-      <x:c r="AL4" s="25"/>
-    </x:row>
-    <x:row r="5" ht="35" customHeight="1">
+      <x:c r="AF4" s="2"/>
+      <x:c r="AG4" s="2"/>
+      <x:c r="AH4" s="2"/>
+      <x:c r="AI4" s="2"/>
+      <x:c r="AJ4" s="2"/>
+      <x:c r="AK4" s="2"/>
+      <x:c r="AL4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="2"/>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -613,17 +629,15 @@
       <x:c r="AC5" s="2"/>
       <x:c r="AD5" s="2"/>
       <x:c r="AE5" s="2"/>
-      <x:c r="AF5" s="25" t="str">
-        <x:v>SDL: https://www.cpf.gov.sg/employer/employer-obligations/skills-development-levy</x:v>
-      </x:c>
-      <x:c r="AG5" s="25"/>
-      <x:c r="AH5" s="25"/>
-      <x:c r="AI5" s="25"/>
-      <x:c r="AJ5" s="25"/>
-      <x:c r="AK5" s="25"/>
-      <x:c r="AL5" s="25"/>
-    </x:row>
-    <x:row r="6" ht="35" customHeight="1">
+      <x:c r="AF5" s="2"/>
+      <x:c r="AG5" s="2"/>
+      <x:c r="AH5" s="2"/>
+      <x:c r="AI5" s="2"/>
+      <x:c r="AJ5" s="2"/>
+      <x:c r="AK5" s="2"/>
+      <x:c r="AL5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="2" t="str">
         <x:v>SGD. August 2026 source baseline. Fictional employees are included for import testing.</x:v>
       </x:c>
@@ -657,17 +671,15 @@
       <x:c r="AC6" s="2"/>
       <x:c r="AD6" s="2"/>
       <x:c r="AE6" s="2"/>
-      <x:c r="AF6" s="25" t="str">
-        <x:v>CPF eligibility and monthly review: https://www.cpf.gov.sg/employer/employer-obligations/who-should-receive-cpf-contributions</x:v>
-      </x:c>
-      <x:c r="AG6" s="25"/>
-      <x:c r="AH6" s="25"/>
-      <x:c r="AI6" s="25"/>
-      <x:c r="AJ6" s="25"/>
-      <x:c r="AK6" s="25"/>
-      <x:c r="AL6" s="25"/>
-    </x:row>
-    <x:row r="7" ht="35" customHeight="1">
+      <x:c r="AF6" s="2"/>
+      <x:c r="AG6" s="2"/>
+      <x:c r="AH6" s="2"/>
+      <x:c r="AI6" s="2"/>
+      <x:c r="AJ6" s="2"/>
+      <x:c r="AK6" s="2"/>
+      <x:c r="AL6" s="2"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="2" t="str">
         <x:v>Proration follows the client: ROUND((basic salary - employee CPF - self-help) / working days * active days, 0).</x:v>
       </x:c>
@@ -701,17 +713,15 @@
       <x:c r="AC7" s="2"/>
       <x:c r="AD7" s="2"/>
       <x:c r="AE7" s="2"/>
-      <x:c r="AF7" s="25" t="str">
-        <x:v>CPF rates and ceilings: https://www.cpf.gov.sg/employer/employer-obligations/how-much-cpf-contributions-to-pay</x:v>
-      </x:c>
-      <x:c r="AG7" s="25"/>
-      <x:c r="AH7" s="25"/>
-      <x:c r="AI7" s="25"/>
-      <x:c r="AJ7" s="25"/>
-      <x:c r="AK7" s="25"/>
-      <x:c r="AL7" s="25"/>
-    </x:row>
-    <x:row r="8" ht="35" customHeight="1">
+      <x:c r="AF7" s="2"/>
+      <x:c r="AG7" s="2"/>
+      <x:c r="AH7" s="2"/>
+      <x:c r="AI7" s="2"/>
+      <x:c r="AJ7" s="2"/>
+      <x:c r="AK7" s="2"/>
+      <x:c r="AL7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="2" t="str">
         <x:v>Medical allowance and other income are added after proration. CPF and self-help amounts require monthly review.</x:v>
       </x:c>
@@ -745,17 +755,15 @@
       <x:c r="AC8" s="2"/>
       <x:c r="AD8" s="2"/>
       <x:c r="AE8" s="2"/>
-      <x:c r="AF8" s="25" t="str">
-        <x:v>Only SDL is automated in this template. CPF, SHG fund eligibility, opt-outs and contribution amounts must be reviewed separately.</x:v>
-      </x:c>
-      <x:c r="AG8" s="25"/>
-      <x:c r="AH8" s="25"/>
-      <x:c r="AI8" s="25"/>
-      <x:c r="AJ8" s="25"/>
-      <x:c r="AK8" s="25"/>
-      <x:c r="AL8" s="25"/>
-    </x:row>
-    <x:row r="9" ht="35" customHeight="1">
+      <x:c r="AF8" s="2"/>
+      <x:c r="AG8" s="2"/>
+      <x:c r="AH8" s="2"/>
+      <x:c r="AI8" s="2"/>
+      <x:c r="AJ8" s="2"/>
+      <x:c r="AK8" s="2"/>
+      <x:c r="AL8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="2" t="str">
         <x:v>SDL uses actual cash wages. Sum employee SDL, then round the employer remittance down to whole dollars.</x:v>
       </x:c>
@@ -789,15 +797,13 @@
       <x:c r="AC9" s="2"/>
       <x:c r="AD9" s="2"/>
       <x:c r="AE9" s="2"/>
-      <x:c r="AF9" s="25" t="str">
-        <x:v>Bonus, leave encashment, tax clearance, benefits, approval matrix, statutory filing and bank export are outside this monthly template.</x:v>
-      </x:c>
-      <x:c r="AG9" s="25"/>
-      <x:c r="AH9" s="25"/>
-      <x:c r="AI9" s="25"/>
-      <x:c r="AJ9" s="25"/>
-      <x:c r="AK9" s="25"/>
-      <x:c r="AL9" s="25"/>
+      <x:c r="AF9" s="2"/>
+      <x:c r="AG9" s="2"/>
+      <x:c r="AH9" s="2"/>
+      <x:c r="AI9" s="2"/>
+      <x:c r="AJ9" s="2"/>
+      <x:c r="AK9" s="2"/>
+      <x:c r="AL9" s="2"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="2" t="str">
@@ -2020,15 +2026,9 @@
     <x:mergeCell ref="AB11:AE11"/>
     <x:mergeCell ref="AF11:AG11"/>
     <x:mergeCell ref="AJ11:AK11"/>
-    <x:mergeCell ref="AF3:AL3"/>
-    <x:mergeCell ref="AF4:AL4"/>
-    <x:mergeCell ref="AF5:AL5"/>
-    <x:mergeCell ref="AF6:AL6"/>
-    <x:mergeCell ref="AF7:AL7"/>
-    <x:mergeCell ref="AF8:AL8"/>
-    <x:mergeCell ref="AF9:AL9"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92a0766c6d54dda"/>
 </x:worksheet>
 </file>
 

--- a/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
+++ b/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="R7e746834a8964907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="R5f0e3d7550584015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="R7c4df82441ad4872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="Rab663c38dcc54305"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="PayrollHeader">'Payroll'!A12:AL12</x:definedName>
@@ -1065,7 +1065,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ13),MIN(MAX(AJ13*$C$4,$G$4),$K$4),AJ13)</x:f>
+        <x:f>IF(T13&gt;0,MIN(MAX(AJ13*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="N13" s="19" t="n">
@@ -1073,11 +1073,11 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="O13" s="19" t="n">
-        <x:f>IF(ISNUMBER(M13),SUM(H13,L13,M13),M13)</x:f>
+        <x:f>IF(T13&gt;0,SUM(H13,L13,M13),"Working days required")</x:f>
         <x:v>25011.25</x:v>
       </x:c>
       <x:c r="P13" s="19" t="n">
-        <x:f>IF(ISNUMBER(O13),O13*12,O13)</x:f>
+        <x:f>IF(T13&gt;0,O13*12,"Working days required")</x:f>
         <x:v>300135</x:v>
       </x:c>
       <x:c r="Q13" s="19" t="n">
@@ -1114,7 +1114,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA13" s="19" t="n">
-        <x:f>IF(ISNUMBER(X13),X13+Z13,X13)</x:f>
+        <x:f>IF(T13&gt;0,X13+Z13,"Working days required")</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="AB13" s="16" t="str"/>
@@ -1142,11 +1142,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ13" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH13),AH13+Y13+Z13,AH13)</x:f>
+        <x:f>IF(T13&gt;0,AH13+Y13+Z13,"Working days required")</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="AK13" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ13),SUM(AJ13,L13,M13),AJ13)</x:f>
+        <x:f>IF(T13&gt;0,SUM(AJ13,L13,M13),"Working days required")</x:f>
         <x:v>25011.25</x:v>
       </x:c>
       <x:c r="AL13" s="19" t="n">
@@ -1188,7 +1188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ14),MIN(MAX(AJ14*$C$4,$G$4),$K$4),AJ14)</x:f>
+        <x:f>IF(T14&gt;0,MIN(MAX(AJ14*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="N14" s="19" t="n">
@@ -1196,11 +1196,11 @@
         <x:v>20970</x:v>
       </x:c>
       <x:c r="O14" s="19" t="n">
-        <x:f>IF(ISNUMBER(M14),SUM(H14,L14,M14),M14)</x:f>
+        <x:f>IF(T14&gt;0,SUM(H14,L14,M14),"Working days required")</x:f>
         <x:v>21011.25</x:v>
       </x:c>
       <x:c r="P14" s="19" t="n">
-        <x:f>IF(ISNUMBER(O14),O14*12,O14)</x:f>
+        <x:f>IF(T14&gt;0,O14*12,"Working days required")</x:f>
         <x:v>252135</x:v>
       </x:c>
       <x:c r="Q14" s="19" t="n">
@@ -1237,7 +1237,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA14" s="19" t="n">
-        <x:f>IF(ISNUMBER(X14),X14+Z14,X14)</x:f>
+        <x:f>IF(T14&gt;0,X14+Z14,"Working days required")</x:f>
         <x:v>20970</x:v>
       </x:c>
       <x:c r="AB14" s="16" t="str"/>
@@ -1265,11 +1265,11 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ14" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH14),AH14+Y14+Z14,AH14)</x:f>
+        <x:f>IF(T14&gt;0,AH14+Y14+Z14,"Working days required")</x:f>
         <x:v>21000</x:v>
       </x:c>
       <x:c r="AK14" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ14),SUM(AJ14,L14,M14),AJ14)</x:f>
+        <x:f>IF(T14&gt;0,SUM(AJ14,L14,M14),"Working days required")</x:f>
         <x:v>21011.25</x:v>
       </x:c>
       <x:c r="AL14" s="19" t="n">
@@ -1311,7 +1311,7 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="M15" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ15),MIN(MAX(AJ15*$C$4,$G$4),$K$4),AJ15)</x:f>
+        <x:f>IF(T15&gt;0,MIN(MAX(AJ15*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>7.0625</x:v>
       </x:c>
       <x:c r="N15" s="19" t="n">
@@ -1319,11 +1319,11 @@
         <x:v>2399</x:v>
       </x:c>
       <x:c r="O15" s="19" t="n">
-        <x:f>IF(ISNUMBER(M15),SUM(H15,L15,M15),M15)</x:f>
+        <x:f>IF(T15&gt;0,SUM(H15,L15,M15),"Working days required")</x:f>
         <x:v>3517.0625</x:v>
       </x:c>
       <x:c r="P15" s="19" t="n">
-        <x:f>IF(ISNUMBER(O15),O15*12,O15)</x:f>
+        <x:f>IF(T15&gt;0,O15*12,"Working days required")</x:f>
         <x:v>42204.75</x:v>
       </x:c>
       <x:c r="Q15" s="19" t="n">
@@ -1360,7 +1360,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AA15" s="19" t="n">
-        <x:f>IF(ISNUMBER(X15),X15+Z15,X15)</x:f>
+        <x:f>IF(T15&gt;0,X15+Z15,"Working days required")</x:f>
         <x:v>2284</x:v>
       </x:c>
       <x:c r="AB15" s="16" t="str"/>
@@ -1388,11 +1388,11 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="AJ15" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH15),AH15+Y15+Z15,AH15)</x:f>
+        <x:f>IF(T15&gt;0,AH15+Y15+Z15,"Working days required")</x:f>
         <x:v>2825</x:v>
       </x:c>
       <x:c r="AK15" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ15),SUM(AJ15,L15,M15),AJ15)</x:f>
+        <x:f>IF(T15&gt;0,SUM(AJ15,L15,M15),"Working days required")</x:f>
         <x:v>3342.0625</x:v>
       </x:c>
       <x:c r="AL15" s="19" t="n">
@@ -1434,7 +1434,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ16),MIN(MAX(AJ16*$C$4,$G$4),$K$4),AJ16)</x:f>
+        <x:f>IF(T16&gt;0,MIN(MAX(AJ16*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="N16" s="19" t="n">
@@ -1442,11 +1442,11 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="O16" s="19" t="n">
-        <x:f>IF(ISNUMBER(M16),SUM(H16,L16,M16),M16)</x:f>
+        <x:f>IF(T16&gt;0,SUM(H16,L16,M16),"Working days required")</x:f>
         <x:v>4011.25</x:v>
       </x:c>
       <x:c r="P16" s="19" t="n">
-        <x:f>IF(ISNUMBER(O16),O16*12,O16)</x:f>
+        <x:f>IF(T16&gt;0,O16*12,"Working days required")</x:f>
         <x:v>48135</x:v>
       </x:c>
       <x:c r="Q16" s="19" t="n">
@@ -1483,7 +1483,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="AA16" s="19" t="n">
-        <x:f>IF(ISNUMBER(X16),X16+Z16,X16)</x:f>
+        <x:f>IF(T16&gt;0,X16+Z16,"Working days required")</x:f>
         <x:v>4550</x:v>
       </x:c>
       <x:c r="AB16" s="16" t="str"/>
@@ -1511,11 +1511,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ16" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH16),AH16+Y16+Z16,AH16)</x:f>
+        <x:f>IF(T16&gt;0,AH16+Y16+Z16,"Working days required")</x:f>
         <x:v>4550</x:v>
       </x:c>
       <x:c r="AK16" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ16),SUM(AJ16,L16,M16),AJ16)</x:f>
+        <x:f>IF(T16&gt;0,SUM(AJ16,L16,M16),"Working days required")</x:f>
         <x:v>4561.25</x:v>
       </x:c>
       <x:c r="AL16" s="19" t="n">
@@ -1557,7 +1557,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ17),MIN(MAX(AJ17*$C$4,$G$4),$K$4),AJ17)</x:f>
+        <x:f>IF(T17&gt;0,MIN(MAX(AJ17*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="N17" s="19" t="n">
@@ -1565,11 +1565,11 @@
         <x:v>609.5</x:v>
       </x:c>
       <x:c r="O17" s="19" t="n">
-        <x:f>IF(ISNUMBER(M17),SUM(H17,L17,M17),M17)</x:f>
+        <x:f>IF(T17&gt;0,SUM(H17,L17,M17),"Working days required")</x:f>
         <x:v>611.5</x:v>
       </x:c>
       <x:c r="P17" s="19" t="n">
-        <x:f>IF(ISNUMBER(O17),O17*12,O17)</x:f>
+        <x:f>IF(T17&gt;0,O17*12,"Working days required")</x:f>
         <x:v>7338</x:v>
       </x:c>
       <x:c r="Q17" s="19" t="n">
@@ -1606,7 +1606,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA17" s="19" t="n">
-        <x:f>IF(ISNUMBER(X17),X17+Z17,X17)</x:f>
+        <x:f>IF(T17&gt;0,X17+Z17,"Working days required")</x:f>
         <x:v>610</x:v>
       </x:c>
       <x:c r="AB17" s="16" t="str"/>
@@ -1634,11 +1634,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ17" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH17),AH17+Y17+Z17,AH17)</x:f>
+        <x:f>IF(T17&gt;0,AH17+Y17+Z17,"Working days required")</x:f>
         <x:v>610</x:v>
       </x:c>
       <x:c r="AK17" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ17),SUM(AJ17,L17,M17),AJ17)</x:f>
+        <x:f>IF(T17&gt;0,SUM(AJ17,L17,M17),"Working days required")</x:f>
         <x:v>612</x:v>
       </x:c>
       <x:c r="AL17" s="19" t="n">
@@ -1680,7 +1680,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ18),MIN(MAX(AJ18*$C$4,$G$4),$K$4),AJ18)</x:f>
+        <x:f>IF(T18&gt;0,MIN(MAX(AJ18*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="N18" s="19" t="n">
@@ -1688,11 +1688,11 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="O18" s="19" t="n">
-        <x:f>IF(ISNUMBER(M18),SUM(H18,L18,M18),M18)</x:f>
+        <x:f>IF(T18&gt;0,SUM(H18,L18,M18),"Working days required")</x:f>
         <x:v>2005</x:v>
       </x:c>
       <x:c r="P18" s="19" t="n">
-        <x:f>IF(ISNUMBER(O18),O18*12,O18)</x:f>
+        <x:f>IF(T18&gt;0,O18*12,"Working days required")</x:f>
         <x:v>24060</x:v>
       </x:c>
       <x:c r="Q18" s="19" t="n">
@@ -1729,7 +1729,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA18" s="19" t="n">
-        <x:f>IF(ISNUMBER(X18),X18+Z18,X18)</x:f>
+        <x:f>IF(T18&gt;0,X18+Z18,"Working days required")</x:f>
         <x:v>2000</x:v>
       </x:c>
       <x:c r="AB18" s="16" t="str"/>
@@ -1757,11 +1757,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ18" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH18),AH18+Y18+Z18,AH18)</x:f>
+        <x:f>IF(T18&gt;0,AH18+Y18+Z18,"Working days required")</x:f>
         <x:v>2000</x:v>
       </x:c>
       <x:c r="AK18" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ18),SUM(AJ18,L18,M18),AJ18)</x:f>
+        <x:f>IF(T18&gt;0,SUM(AJ18,L18,M18),"Working days required")</x:f>
         <x:v>2005</x:v>
       </x:c>
       <x:c r="AL18" s="19" t="n">
@@ -1803,7 +1803,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ19),MIN(MAX(AJ19*$C$4,$G$4),$K$4),AJ19)</x:f>
+        <x:f>IF(T19&gt;0,MIN(MAX(AJ19*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="N19" s="19" t="n">
@@ -1811,11 +1811,11 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="O19" s="19" t="n">
-        <x:f>IF(ISNUMBER(M19),SUM(H19,L19,M19),M19)</x:f>
+        <x:f>IF(T19&gt;0,SUM(H19,L19,M19),"Working days required")</x:f>
         <x:v>4511.25</x:v>
       </x:c>
       <x:c r="P19" s="19" t="n">
-        <x:f>IF(ISNUMBER(O19),O19*12,O19)</x:f>
+        <x:f>IF(T19&gt;0,O19*12,"Working days required")</x:f>
         <x:v>54135</x:v>
       </x:c>
       <x:c r="Q19" s="19" t="n">
@@ -1852,7 +1852,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA19" s="19" t="n">
-        <x:f>IF(ISNUMBER(X19),X19+Z19,X19)</x:f>
+        <x:f>IF(T19&gt;0,X19+Z19,"Working days required")</x:f>
         <x:v>4500</x:v>
       </x:c>
       <x:c r="AB19" s="16" t="str"/>
@@ -1880,11 +1880,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ19" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH19),AH19+Y19+Z19,AH19)</x:f>
+        <x:f>IF(T19&gt;0,AH19+Y19+Z19,"Working days required")</x:f>
         <x:v>4500</x:v>
       </x:c>
       <x:c r="AK19" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ19),SUM(AJ19,L19,M19),AJ19)</x:f>
+        <x:f>IF(T19&gt;0,SUM(AJ19,L19,M19),"Working days required")</x:f>
         <x:v>4511.25</x:v>
       </x:c>
       <x:c r="AL19" s="19" t="n">
@@ -1926,7 +1926,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M20" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ20),MIN(MAX(AJ20*$C$4,$G$4),$K$4),AJ20)</x:f>
+        <x:f>IF(T20&gt;0,MIN(MAX(AJ20*$C$4,$G$4),$K$4),"Working days required")</x:f>
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="N20" s="19" t="n">
@@ -1934,11 +1934,11 @@
         <x:v>4502.03</x:v>
       </x:c>
       <x:c r="O20" s="19" t="n">
-        <x:f>IF(ISNUMBER(M20),SUM(H20,L20,M20),M20)</x:f>
+        <x:f>IF(T20&gt;0,SUM(H20,L20,M20),"Working days required")</x:f>
         <x:v>4513.28</x:v>
       </x:c>
       <x:c r="P20" s="19" t="n">
-        <x:f>IF(ISNUMBER(O20),O20*12,O20)</x:f>
+        <x:f>IF(T20&gt;0,O20*12,"Working days required")</x:f>
         <x:v>54159.36</x:v>
       </x:c>
       <x:c r="Q20" s="19" t="n">
@@ -1975,7 +1975,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA20" s="19" t="n">
-        <x:f>IF(ISNUMBER(X20),X20+Z20,X20)</x:f>
+        <x:f>IF(T20&gt;0,X20+Z20,"Working days required")</x:f>
         <x:v>4502</x:v>
       </x:c>
       <x:c r="AB20" s="16" t="str"/>
@@ -2003,11 +2003,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AJ20" s="19" t="n">
-        <x:f>IF(ISNUMBER(AH20),AH20+Y20+Z20,AH20)</x:f>
+        <x:f>IF(T20&gt;0,AH20+Y20+Z20,"Working days required")</x:f>
         <x:v>4502</x:v>
       </x:c>
       <x:c r="AK20" s="19" t="n">
-        <x:f>IF(ISNUMBER(AJ20),SUM(AJ20,L20,M20),AJ20)</x:f>
+        <x:f>IF(T20&gt;0,SUM(AJ20,L20,M20),"Working days required")</x:f>
         <x:v>4513.25</x:v>
       </x:c>
       <x:c r="AL20" s="19" t="n">
@@ -2028,7 +2028,7 @@
     <x:mergeCell ref="AJ11:AK11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92a0766c6d54dda"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e9f091152143a1"/>
 </x:worksheet>
 </file>
 

--- a/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
+++ b/outputs/sg-payroll-20261014/Rize_Singapore_Payroll_Configuration_Aug2026.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="R7c4df82441ad4872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="Rab663c38dcc54305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="1" r:id="Rb270b4bbf2de48fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Map" sheetId="2" r:id="Rbc57b3584a354cc5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="PayrollHeader">'Payroll'!A12:AL12</x:definedName>
@@ -2028,7 +2028,7 @@
     <x:mergeCell ref="AJ11:AK11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e9f091152143a1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29ab5da01e634816"/>
 </x:worksheet>
 </file>
 
